--- a/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,92</t>
+          <t>3,92; 6,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,81; 25,01</t>
+          <t>18,87; 25,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,63</t>
+          <t>10,64; 17,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,09</t>
+          <t>4,43; 7,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 23,59</t>
+          <t>18,1; 23,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 13,99</t>
+          <t>10,32; 13,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,52</t>
+          <t>4,52; 6,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,41; 23,33</t>
+          <t>19,23; 23,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 14,21</t>
+          <t>10,96; 14,37</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,11</t>
+          <t>3,13; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,08</t>
+          <t>13,85; 17,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,22</t>
+          <t>6,79; 12,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,19</t>
+          <t>3,3; 5,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,03</t>
+          <t>10,93; 14,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 22,29</t>
+          <t>8,98; 22,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 4,81</t>
+          <t>3,5; 4,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 15,02</t>
+          <t>12,78; 14,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 15,79</t>
+          <t>9,18; 16,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,59</t>
+          <t>1,35; 4,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,0</t>
+          <t>6,58; 11,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,69</t>
+          <t>6,59; 11,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,23</t>
+          <t>1,12; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,48</t>
+          <t>7,94; 13,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,98</t>
+          <t>8,47; 12,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,66</t>
+          <t>1,5; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,49</t>
+          <t>8,08; 11,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,63</t>
+          <t>8,2; 11,43</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,87</t>
+          <t>3,49; 4,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 17,1</t>
+          <t>14,55; 17,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 11,82</t>
+          <t>8,12; 11,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,22</t>
+          <t>3,87; 5,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 15,77</t>
+          <t>13,36; 15,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 18,29</t>
+          <t>9,91; 17,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,82</t>
+          <t>3,84; 4,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,07</t>
+          <t>14,31; 16,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,41</t>
+          <t>9,79; 14,21</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37809; 67417</t>
+          <t>38198; 66042</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>141918; 188644</t>
+          <t>142334; 189113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53425; 85629</t>
+          <t>54783; 87569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60048; 94800</t>
+          <t>59278; 94231</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>182182; 234599</t>
+          <t>180077; 233633</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78899; 105696</t>
+          <t>77956; 104135</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>105809; 150851</t>
+          <t>104459; 149083</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>339471; 408032</t>
+          <t>336252; 404797</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>138248; 180516</t>
+          <t>139202; 182554</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61685; 100323</t>
+          <t>61387; 98688</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>282042; 354716</t>
+          <t>287533; 354680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168671; 279932</t>
+          <t>155549; 281723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56972; 91290</t>
+          <t>58023; 92706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>218564; 278956</t>
+          <t>217305; 278738</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>195955; 498810</t>
+          <t>200922; 495822</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>126065; 179116</t>
+          <t>130251; 177915</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>520659; 610597</t>
+          <t>519531; 609436</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>418796; 715207</t>
+          <t>415815; 729086</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6040; 22101</t>
+          <t>6515; 23147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35566; 65622</t>
+          <t>35959; 65373</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42905; 75576</t>
+          <t>42592; 75876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5017; 19401</t>
+          <t>5144; 19864</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44319; 74036</t>
+          <t>43593; 71963</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55605; 85706</t>
+          <t>55926; 84588</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13547; 34434</t>
+          <t>14092; 35192</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86882; 125932</t>
+          <t>88562; 129585</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106121; 151956</t>
+          <t>107132; 149349</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>117502; 166579</t>
+          <t>119311; 168965</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>487341; 577691</t>
+          <t>491340; 575975</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>288669; 407949</t>
+          <t>280221; 412513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135365; 185471</t>
+          <t>137454; 187183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>468625; 557047</t>
+          <t>471900; 553808</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>355014; 668372</t>
+          <t>361975; 650227</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>268796; 336416</t>
+          <t>268049; 340093</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>986121; 1110421</t>
+          <t>988780; 1118834</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>707667; 1023844</t>
+          <t>695369; 1009484</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -51,34 +51,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -505,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,12 +485,6 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,67 +499,31 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -605,12 +535,6 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,47 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -678,47 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,78</t>
+          <t>11,41; 17,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 25,07</t>
+          <t>11,1; 14,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 17,01</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,43; 7,04</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,1; 23,49</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,32; 13,78</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,52; 6,45</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19,23; 23,14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10,96; 14,37</t>
+          <t>12,04; 15,17</t>
         </is>
       </c>
     </row>
@@ -735,47 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -788,47 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,02</t>
+          <t>10,74; 14,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,85; 17,08</t>
+          <t>11,14; 13,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 12,3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3,3; 5,27</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,93; 14,02</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,98; 22,16</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,5; 4,78</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 14,99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 16,1</t>
+          <t>11,26; 13,38</t>
         </is>
       </c>
     </row>
@@ -845,47 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -898,47 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,81</t>
+          <t>8,2; 13,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,95</t>
+          <t>9,1; 13,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,73</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 4,33</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,94; 13,1</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,47; 12,81</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 3,74</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8,08; 11,82</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>8,2; 11,43</t>
+          <t>9,31; 12,6</t>
         </is>
       </c>
     </row>
@@ -955,47 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,94</t>
+          <t>11,0; 13,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 17,05</t>
+          <t>11,21; 13,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3,87; 5,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,36; 15,68</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,91; 17,8</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,84; 4,88</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14,31; 16,19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9,79; 14,21</t>
+          <t>11,45; 13,03</t>
         </is>
       </c>
     </row>
@@ -1060,12 +744,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C1:E1"/>
+  <mergeCells count="5">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
@@ -1080,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1088,12 +769,6 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,67 +783,31 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1180,12 +819,6 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1200,45 +833,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>166</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>248</t>
         </is>
@@ -1253,47 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>164978</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68152</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>75781</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>206778</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91061</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>126113</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>371755</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>159213</t>
+          <t>187704</t>
         </is>
       </c>
     </row>
@@ -1306,47 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38198; 66042</t>
+          <t>66038; 102052</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>142334; 189113</t>
+          <t>91250; 121934</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54783; 87569</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>59278; 94231</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>180077; 233633</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>77956; 104135</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>104459; 149083</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>336252; 404797</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139202; 182554</t>
+          <t>168613; 212479</t>
         </is>
       </c>
     </row>
@@ -1363,45 +906,15 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>566</t>
         </is>
@@ -1416,47 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>79885</t>
+          <t>272865</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>318894</t>
+          <t>268239</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>233623</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73407</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>246848</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>282914</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>153292</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>565743</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>516537</t>
+          <t>541103</t>
         </is>
       </c>
     </row>
@@ -1469,47 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61387; 98688</t>
+          <t>239490; 313842</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>287533; 354680</t>
+          <t>241789; 299256</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155549; 281723</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58023; 92706</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>217305; 278738</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>200922; 495822</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>130251; 177915</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>519531; 609436</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>415815; 729086</t>
+          <t>495858; 589057</t>
         </is>
       </c>
     </row>
@@ -1526,45 +979,15 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>163</t>
         </is>
@@ -1579,47 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>76114</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48650</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57579</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10387</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>57798</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69265</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22286</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>106448</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>126844</t>
+          <t>157948</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6515; 23147</t>
+          <t>58355; 99032</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35959; 65373</t>
+          <t>66906; 98415</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42592; 75876</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5144; 19864</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>43593; 71963</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>55926; 84588</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14092; 35192</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>88562; 129585</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>107132; 149349</t>
+          <t>134638; 182316</t>
         </is>
       </c>
     </row>
@@ -1689,45 +1052,15 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>977</t>
         </is>
@@ -1742,47 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>142116</t>
+          <t>431293</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>532522</t>
+          <t>455462</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359354</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159575</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>511424</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>443240</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>301691</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1043946</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>802593</t>
+          <t>886755</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>119311; 168965</t>
+          <t>387136; 473666</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>491340; 575975</t>
+          <t>417850; 492382</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>280221; 412513</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>137454; 187183</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>471900; 553808</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>361975; 650227</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>268049; 340093</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>988780; 1118834</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>695369; 1009484</t>
+          <t>830266; 944417</t>
         </is>
       </c>
     </row>
@@ -1847,13 +1120,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C1:E1"/>
+  <mergeCells count="5">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,41; 17,64</t>
+          <t>40,25; 48,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,1; 14,83</t>
+          <t>45,79; 51,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 15,17</t>
+          <t>44,59; 49,29</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 14,07</t>
+          <t>35,66; 40,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 13,78</t>
+          <t>38,12; 42,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 13,38</t>
+          <t>37,6; 40,71</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 13,92</t>
+          <t>32,1; 39,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,39</t>
+          <t>31,89; 38,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 12,6</t>
+          <t>32,95; 37,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,45</t>
+          <t>36,89; 40,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,21</t>
+          <t>39,53; 42,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 13,03</t>
+          <t>38,78; 41,09</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -833,17 +833,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>312</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>649</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>961</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82314</t>
+          <t>255699</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>105389</t>
+          <t>400364</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187704</t>
+          <t>656063</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66038; 102052</t>
+          <t>232849; 279072</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91250; 121934</t>
+          <t>376451; 421920</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168613; 212479</t>
+          <t>624530; 690382</t>
         </is>
       </c>
     </row>
@@ -906,17 +906,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>763</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>1843</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>272865</t>
+          <t>850592</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>268239</t>
+          <t>869866</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>541103</t>
+          <t>1720458</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>239490; 313842</t>
+          <t>795003; 901030</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>241789; 299256</t>
+          <t>827479; 914480</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>495858; 589057</t>
+          <t>1654436; 1791123</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>579</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>253520</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81834</t>
+          <t>256792</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157948</t>
+          <t>510312</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>58355; 99032</t>
+          <t>227178; 281053</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66906; 98415</t>
+          <t>233554; 280891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134638; 182316</t>
+          <t>474545; 546603</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>3383</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>431293</t>
+          <t>1359811</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>455462</t>
+          <t>1527022</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886755</t>
+          <t>2886833</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>387136; 473666</t>
+          <t>1297045; 1427564</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>417850; 492382</t>
+          <t>1472522; 1584714</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>830266; 944417</t>
+          <t>2807963; 2975442</t>
         </is>
       </c>
     </row>
